--- a/docs/oc-mensuales/venta-y-arriendo-de-computadores-y-accesorios/feb-2026.xlsx
+++ b/docs/oc-mensuales/venta-y-arriendo-de-computadores-y-accesorios/feb-2026.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M189"/>
+  <dimension ref="A1:M186"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5760,7 +5760,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2701-77-CM26</t>
+          <t>1426038-27-CM26</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>69.071.800-6</t>
+          <t>70.941.900-5</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALAGANTE</t>
+          <t>CORPORACION MUNICIPAL DE DESARROLLO SOCIAL COLINA</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -5800,12 +5800,12 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>COMPUNOW SPA</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>78.218.816-K</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K88" t="inlineStr"/>
@@ -5815,7 +5815,7 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>3732.39</v>
+        <v>967.47</v>
       </c>
     </row>
     <row r="89">
@@ -6004,7 +6004,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>1426038-27-CM26</t>
+          <t>2701-77-CM26</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -6029,12 +6029,12 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>70.941.900-5</t>
+          <t>69.071.800-6</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE DESARROLLO SOCIAL COLINA</t>
+          <t>I MUNICIPALIDAD DE TALAGANTE</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -6044,12 +6044,12 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>COMPUNOW SPA</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>78.218.816-K</t>
         </is>
       </c>
       <c r="K92" t="inlineStr"/>
@@ -6059,13 +6059,13 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>967.47</v>
+        <v>3732.39</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>1035685-26-CM26</t>
+          <t>3232-86-CM26</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -6090,27 +6090,27 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>62.000.400-6</t>
+          <t>69.073.500-8</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>CENTRO DE FORMACION TECNICA ESTATAL DE LA REGION DE LOS RIOS</t>
+          <t>I MUNICIPALIDAD DE SANTO DOMINGO</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>COMPUNOW SPA</t>
+          <t>RICOH</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>78.218.816-K</t>
+          <t>96.513.980-k</t>
         </is>
       </c>
       <c r="K93" t="inlineStr"/>
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>64193.03</v>
+        <v>597.12</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>3232-86-CM26</t>
+          <t>1035685-26-CM26</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -6151,27 +6151,27 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>69.073.500-8</t>
+          <t>62.000.400-6</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SANTO DOMINGO</t>
+          <t>CENTRO DE FORMACION TECNICA ESTATAL DE LA REGION DE LOS RIOS</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>RICOH</t>
+          <t>COMPUNOW SPA</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>96.513.980-k</t>
+          <t>78.218.816-K</t>
         </is>
       </c>
       <c r="K94" t="inlineStr"/>
@@ -6181,7 +6181,7 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>597.12</v>
+        <v>64193.03</v>
       </c>
     </row>
     <row r="95">
@@ -6309,7 +6309,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>3232-80-CM26</t>
+          <t>2407-90-CM26</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -6329,32 +6329,32 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Cancelada</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>69.073.500-8</t>
+          <t>69.071.200-8</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SANTO DOMINGO</t>
+          <t>I MUNICIPALIDAD DE RENCA</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TODOCLICK SPA</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>76.977.985-K</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K97" t="inlineStr"/>
@@ -6364,13 +6364,13 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>19170.66</v>
+        <v>2917.37</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2407-90-CM26</t>
+          <t>1375761-43-CM26</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -6390,17 +6390,17 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>69.071.200-8</t>
+          <t>61.981.330-8</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RENCA</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA VALLE DIGUILLÍN</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -6410,12 +6410,12 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>BOOKCOMPUTER</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>76.376.530-k</t>
         </is>
       </c>
       <c r="K98" t="inlineStr"/>
@@ -6425,13 +6425,13 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>2917.37</v>
+        <v>75659.37</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>1375761-43-CM26</t>
+          <t>4964-16-CM26</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -6456,17 +6456,17 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>61.981.330-8</t>
+          <t>69.061.400-6</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA VALLE DIGUILLÍN</t>
+          <t>I MUNICIPALIDAD DE CASABLANCA</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -6486,13 +6486,13 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>75659.37</v>
+        <v>2829.34</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>4964-16-CM26</t>
+          <t>4931-28-CM26</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -6507,7 +6507,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -6517,27 +6517,27 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>69.061.400-6</t>
+          <t>65.613.130-6</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CASABLANCA</t>
+          <t>COMISION ADMINISTRADORA DEL SISTEMA DE CREDITOS P. ESTUDIOS SUPERIORES</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER</t>
+          <t>COMERCIALIZADORA IGESCOM SPA</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>76.376.530-k</t>
+          <t>77.152.668-3</t>
         </is>
       </c>
       <c r="K100" t="inlineStr"/>
@@ -6547,13 +6547,13 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>2829.34</v>
+        <v>371.28</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>4931-28-CM26</t>
+          <t>1305532-6-CM26</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -6578,12 +6578,12 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>65.613.130-6</t>
+          <t>61.981.040-6</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>COMISION ADMINISTRADORA DEL SISTEMA DE CREDITOS P. ESTUDIOS SUPERIORES</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DEL ELQUI</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -6593,12 +6593,12 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA IGESCOM SPA</t>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>77.152.668-3</t>
+          <t>76.799.430-3</t>
         </is>
       </c>
       <c r="K101" t="inlineStr"/>
@@ -6608,13 +6608,13 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>371.28</v>
+        <v>7255.43</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>1305532-6-CM26</t>
+          <t>1084156-100-CM26</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -6639,17 +6639,17 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>61.981.040-6</t>
+          <t>65.181.672-6</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DEL ELQUI</t>
+          <t>SERVICIO LOCAL DE EDUCACION PUBLICA ANDALIEN SUR</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Bío-Bío</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -6669,13 +6669,13 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>7255.43</v>
+        <v>14916.03</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>1084156-100-CM26</t>
+          <t>603663-27-CM26</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -6700,27 +6700,27 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>65.181.672-6</t>
+          <t>65.028.707-K</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION PUBLICA ANDALIEN SUR</t>
+          <t>INSTITUTO NACIONAL DE DERECHOS HUMANOS</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>76.799.430-3</t>
+          <t>77.474.803-2</t>
         </is>
       </c>
       <c r="K103" t="inlineStr"/>
@@ -6730,13 +6730,13 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>14916.03</v>
+        <v>3499.65</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>603663-27-CM26</t>
+          <t>2013-176-CM26</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -6756,32 +6756,32 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>65.028.707-K</t>
+          <t>70.777.500-9</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DERECHOS HUMANOS</t>
+          <t>UNIVERSIDAD ARTURO PRAT</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+          <t>SOC INFORMATICA SIGLO 21 LIMITADA</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>77.474.803-2</t>
+          <t>76.179.170-2</t>
         </is>
       </c>
       <c r="K104" t="inlineStr"/>
@@ -6791,13 +6791,13 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>3499.65</v>
+        <v>6806.8</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2013-176-CM26</t>
+          <t>2792-70-CM26</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -6822,17 +6822,17 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>70.777.500-9</t>
+          <t>69.255.400-0</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD ARTURO PRAT</t>
+          <t>Iluste Municipalidad de Huechuraba</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -6852,13 +6852,13 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>6806.8</v>
+        <v>1029.23</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2792-70-CM26</t>
+          <t>5153-41-CM26</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -6883,12 +6883,12 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>69.255.400-0</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Iluste Municipalidad de Huechuraba</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -6898,12 +6898,12 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>SOC INFORMATICA SIGLO 21 LIMITADA</t>
+          <t>FRANCO</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>76.179.170-2</t>
+          <t>76.139.769-9</t>
         </is>
       </c>
       <c r="K106" t="inlineStr"/>
@@ -6913,13 +6913,13 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>1029.23</v>
+        <v>2314.55</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>5153-41-CM26</t>
+          <t>2013-187-CM26</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -6944,27 +6944,27 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>70.777.500-9</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>UNIVERSIDAD ARTURO PRAT</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>FRANCO</t>
+          <t>Sumatec Ltda.</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>76.139.769-9</t>
+          <t>76.367.430-4</t>
         </is>
       </c>
       <c r="K107" t="inlineStr"/>
@@ -6974,13 +6974,13 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>2314.55</v>
+        <v>3070.2</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2013-187-CM26</t>
+          <t>2410-53-CM26</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -6995,37 +6995,37 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>70.777.500-9</t>
+          <t>69.170.102-6</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD ARTURO PRAT</t>
+          <t>MUNICIPALIDAD DE LOS ANGELES AREA SALUD</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Bío-Bío</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>Sumatec Ltda.</t>
+          <t>SANDOS SPA</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>76.367.430-4</t>
+          <t>77.319.537-4</t>
         </is>
       </c>
       <c r="K108" t="inlineStr"/>
@@ -7035,13 +7035,13 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>3070.2</v>
+        <v>52037.21</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2410-53-CM26</t>
+          <t>1375761-40-CM26</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -7066,27 +7066,27 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>69.170.102-6</t>
+          <t>61.981.330-8</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE LOS ANGELES AREA SALUD</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA VALLE DIGUILLÍN</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>SANDOS SPA</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>77.319.537-4</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K109" t="inlineStr"/>
@@ -7096,13 +7096,13 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>52037.21</v>
+        <v>8701.049999999999</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>1375761-40-CM26</t>
+          <t>2792-75-CM26</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -7122,17 +7122,17 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>61.981.330-8</t>
+          <t>69.255.400-0</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA VALLE DIGUILLÍN</t>
+          <t>Iluste Municipalidad de Huechuraba</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -7142,12 +7142,12 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>SOC INFORMATICA SIGLO 21 LIMITADA</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>76.179.170-2</t>
         </is>
       </c>
       <c r="K110" t="inlineStr"/>
@@ -7157,13 +7157,13 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>8701.049999999999</v>
+        <v>2058.46</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2792-75-CM26</t>
+          <t>539119-469-CM26</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -7183,17 +7183,17 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>69.255.400-0</t>
+          <t>60.505.720-9</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Iluste Municipalidad de Huechuraba</t>
+          <t>Carabineros de Chile - Dirección de Bienestar</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -7203,12 +7203,12 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>SOC INFORMATICA SIGLO 21 LIMITADA</t>
+          <t>Ingenieria y Tecnologia Kropsys Ltda.</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>76.179.170-2</t>
+          <t>76.095.533-7</t>
         </is>
       </c>
       <c r="K111" t="inlineStr"/>
@@ -7218,13 +7218,13 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>2058.46</v>
+        <v>2565.31</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>539119-469-CM26</t>
+          <t>3766-33-CM26</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -7239,7 +7239,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -7249,27 +7249,27 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>60.505.720-9</t>
+          <t>69.110.600-4</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Dirección de Bienestar</t>
+          <t>I MUNICIPALIDAD DE PELARCO</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>Ingenieria y Tecnologia Kropsys Ltda.</t>
+          <t>BOOKCOMPUTER</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>76.095.533-7</t>
+          <t>76.376.530-k</t>
         </is>
       </c>
       <c r="K112" t="inlineStr"/>
@@ -7279,13 +7279,13 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>2565.31</v>
+        <v>5200.7</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>4099-101-CM26</t>
+          <t>1456840-2-CM26</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -7310,27 +7310,27 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>69.073.300-5</t>
+          <t>61.981.460-6</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MARIA PINTO</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DEL RELONCAVÍ</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Bío-Bío</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K113" t="inlineStr"/>
@@ -7340,13 +7340,13 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>8662.610000000001</v>
+        <v>65795.10000000001</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>1456840-2-CM26</t>
+          <t>4099-101-CM26</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -7371,27 +7371,27 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>61.981.460-6</t>
+          <t>69.073.300-5</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DEL RELONCAVÍ</t>
+          <t>I MUNICIPALIDAD DE MARIA PINTO</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K114" t="inlineStr"/>
@@ -7401,13 +7401,13 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>65795.10000000001</v>
+        <v>8662.610000000001</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>3766-33-CM26</t>
+          <t>2710-64-CM26</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -7432,27 +7432,27 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>69.110.600-4</t>
+          <t>69.040.700-0</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PELARCO</t>
+          <t>MUNICIPALIDAD DE OVALLE</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER</t>
+          <t>COMPUNOW SPA</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>76.376.530-k</t>
+          <t>78.218.816-K</t>
         </is>
       </c>
       <c r="K115" t="inlineStr"/>
@@ -7462,13 +7462,13 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>5200.7</v>
+        <v>39890.93</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>3693-15-CM26</t>
+          <t>3693-13-CM26</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -7508,12 +7508,12 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>COMPUNOW SPA</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>78.218.816-K</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K116" t="inlineStr"/>
@@ -7523,13 +7523,13 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>29516.9</v>
+        <v>5537.03</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>3693-13-CM26</t>
+          <t>1456841-3-CM26</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -7549,22 +7549,22 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>69.061.700-5</t>
+          <t>61.981.470-3</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE EL QUISCO</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA TALAGANTE</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -7584,13 +7584,13 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>5537.03</v>
+        <v>7767.71</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>1456841-3-CM26</t>
+          <t>3693-15-CM26</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -7610,32 +7610,32 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>61.981.470-3</t>
+          <t>69.061.700-5</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA TALAGANTE</t>
+          <t>I MUNICIPALIDAD DE EL QUISCO</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>COMPUNOW SPA</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>78.218.816-K</t>
         </is>
       </c>
       <c r="K118" t="inlineStr"/>
@@ -7645,13 +7645,13 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>7767.71</v>
+        <v>29516.9</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2710-64-CM26</t>
+          <t>3863-58-CM26</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -7666,7 +7666,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -7676,27 +7676,27 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>69.040.700-0</t>
+          <t>69.090.600-7</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE OVALLE</t>
+          <t>I MUNICIPALIDAD DE SANTA CRUZ</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Lib. Gral. Bdo. O'Higgins</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>COMPUNOW SPA</t>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>78.218.816-K</t>
+          <t>76.799.430-3</t>
         </is>
       </c>
       <c r="K119" t="inlineStr"/>
@@ -7706,13 +7706,13 @@
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>39890.93</v>
+        <v>12178.46</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>3892-71-CM26</t>
+          <t>1339159-18-CM26</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -7732,32 +7732,32 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>69.160.300-8</t>
+          <t>61.981.070-8</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LEBU</t>
+          <t>Servicio Local de Educación Pública Santa Rosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>Sumatec Ltda.</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>76.367.430-4</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K120" t="inlineStr"/>
@@ -7767,13 +7767,13 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>3361.63</v>
+        <v>72738.75</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>3863-58-CM26</t>
+          <t>1618-63-CM26</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -7798,27 +7798,27 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>69.090.600-7</t>
+          <t>60.802.000-4</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SANTA CRUZ</t>
+          <t>DIRECCION DE PRESUPUESTOS MINISTERIO DE</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+          <t>Tic Services SPA</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>76.799.430-3</t>
+          <t>76.423.634-3</t>
         </is>
       </c>
       <c r="K121" t="inlineStr"/>
@@ -7828,13 +7828,13 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>12178.46</v>
+        <v>21487</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>1339159-18-CM26</t>
+          <t>3892-70-CM26</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -7854,32 +7854,32 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>61.981.070-8</t>
+          <t>69.160.300-8</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Santa Rosa</t>
+          <t>I MUNICIPALIDAD DE LEBU</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Bío-Bío</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K122" t="inlineStr"/>
@@ -7889,13 +7889,13 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>72738.75</v>
+        <v>2598.78</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>1618-63-CM26</t>
+          <t>3882-66-CM26</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -7920,27 +7920,27 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>60.802.000-4</t>
+          <t>69.060.400-0</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>DIRECCION DE PRESUPUESTOS MINISTERIO DE</t>
+          <t>I MUNICIPALIDAD DE LLAY LLAY</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>Tic Services SPA</t>
+          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>76.423.634-3</t>
+          <t>77.108.316-1</t>
         </is>
       </c>
       <c r="K123" t="inlineStr"/>
@@ -7950,13 +7950,13 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>21487</v>
+        <v>8488.030000000001</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>3892-70-CM26</t>
+          <t>1305544-15-CM26</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -7981,27 +7981,27 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>69.160.300-8</t>
+          <t>61.981.080-5</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LEBU</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA SANTA CORINA</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K124" t="inlineStr"/>
@@ -8011,13 +8011,13 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>2598.78</v>
+        <v>14610.23</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>3882-66-CM26</t>
+          <t>3892-71-CM26</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -8037,32 +8037,32 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>69.060.400-0</t>
+          <t>69.160.300-8</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LLAY LLAY</t>
+          <t>I MUNICIPALIDAD DE LEBU</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Bío-Bío</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
+          <t>Sumatec Ltda.</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>77.108.316-1</t>
+          <t>76.367.430-4</t>
         </is>
       </c>
       <c r="K125" t="inlineStr"/>
@@ -8072,13 +8072,13 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>8488.030000000001</v>
+        <v>3361.63</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>1305544-15-CM26</t>
+          <t>2297-169-CM26</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -8103,27 +8103,27 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>61.981.080-5</t>
+          <t>69.210.100-6</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA SANTA CORINA</t>
+          <t>I MUNICIPALIDAD DE OSORNO</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K126" t="inlineStr"/>
@@ -8133,13 +8133,13 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>14610.23</v>
+        <v>967.47</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>5520-1152-CM26</t>
+          <t>3872-39-CM26</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -8154,37 +8154,37 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Cancelada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>69.040.900-3</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>I MUNICIPALIDAD DE PUNITAQUI</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TODOCLICK SPA</t>
+          <t>PC FACTORY</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>76.977.985-K</t>
+          <t>78.885.550-8</t>
         </is>
       </c>
       <c r="K127" t="inlineStr"/>
@@ -8194,13 +8194,13 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>18492.24</v>
+        <v>1594.36</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2297-169-CM26</t>
+          <t>1237328-44-CM26</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -8215,7 +8215,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -8225,43 +8225,47 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>69.210.100-6</t>
+          <t>70.931.900-0</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE OSORNO</t>
+          <t>CORP MUNICIPAL DE PUNTA ARENAS PARA LA EDUCACION SALUD Y AT AL MENOR</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Magallanes y Antártica</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>COMERCIALIZADORA TECNOIMPORT SPA</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
-        </is>
-      </c>
-      <c r="K128" t="inlineStr"/>
+          <t>77.168.105-0</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
       <c r="L128" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>967.47</v>
+        <v>95038.72</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>3872-39-CM26</t>
+          <t>3679-65-CM26</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -8286,27 +8290,27 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>69.040.900-3</t>
+          <t>69.051.400-1</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUNITAQUI</t>
+          <t>I MUNICIPALIDAD DE SAN ESTEBAN</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>PC FACTORY</t>
+          <t>COMERCIALIZADORA TODOCLICK SPA</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>78.885.550-8</t>
+          <t>76.977.985-K</t>
         </is>
       </c>
       <c r="K129" t="inlineStr"/>
@@ -8316,13 +8320,13 @@
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>1594.36</v>
+        <v>616.41</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2297-177-CM26</t>
+          <t>1417913-174-CM26</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -8347,27 +8351,27 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>69.210.100-6</t>
+          <t>70.938.800-2</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE OSORNO</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE IQUIQUE</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>COMPUNOW SPA</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>78.218.816-K</t>
         </is>
       </c>
       <c r="K130" t="inlineStr"/>
@@ -8377,13 +8381,13 @@
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>967.47</v>
+        <v>3219</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>4832-117-CM26</t>
+          <t>2297-177-CM26</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -8403,17 +8407,17 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>69.252.000-9</t>
+          <t>69.210.100-6</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD COCHAMO</t>
+          <t>I MUNICIPALIDAD DE OSORNO</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -8423,12 +8427,12 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>96.523.180-3</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K131" t="inlineStr"/>
@@ -8438,13 +8442,13 @@
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>3807.99</v>
+        <v>967.47</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>3679-65-CM26</t>
+          <t>4832-117-CM26</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -8469,27 +8473,27 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>69.051.400-1</t>
+          <t>69.252.000-9</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN ESTEBAN</t>
+          <t>ILUSTRE MUNICIPALIDAD COCHAMO</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TODOCLICK SPA</t>
+          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>76.977.985-K</t>
+          <t>96.523.180-3</t>
         </is>
       </c>
       <c r="K132" t="inlineStr"/>
@@ -8499,13 +8503,13 @@
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>616.41</v>
+        <v>3807.99</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>1237328-44-CM26</t>
+          <t>975-49-CM26</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -8520,7 +8524,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -8530,47 +8534,43 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>70.931.900-0</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE PUNTA ARENAS PARA LA EDUCACION SALUD Y AT AL MENOR</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TECNOIMPORT SPA</t>
+          <t>BOOKCOMPUTER</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>77.168.105-0</t>
-        </is>
-      </c>
-      <c r="K133" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+          <t>76.376.530-k</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr"/>
       <c r="L133" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>95038.7193</v>
+        <v>14236.51</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>1417913-174-CM26</t>
+          <t>1305504-22-CM26</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -8585,37 +8585,37 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>70.938.800-2</t>
+          <t>61.981.100-3</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE IQUIQUE</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE ANDALIÉN CO</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Bío-Bío</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>COMPUNOW SPA</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>78.218.816-K</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K134" t="inlineStr"/>
@@ -8625,7 +8625,7 @@
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>3219</v>
+        <v>4145.48</v>
       </c>
     </row>
     <row r="135">
@@ -8692,7 +8692,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>975-49-CM26</t>
+          <t>4494-79-CM26</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -8717,27 +8717,27 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>69.150.500-6</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>I MUNICIPALIDAD DE PENCO</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Bío-Bío</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER</t>
+          <t>SOC INFORMATICA SIGLO 21 LIMITADA</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>76.376.530-k</t>
+          <t>76.179.170-2</t>
         </is>
       </c>
       <c r="K136" t="inlineStr"/>
@@ -8747,13 +8747,13 @@
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>14236.51</v>
+        <v>6918.66</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>1305504-22-CM26</t>
+          <t>1057545-161-CM26</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -8778,27 +8778,27 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>61.981.100-3</t>
+          <t>61.607.500-4</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE ANDALIÉN CO</t>
+          <t>SERVICIO DE SALUD LOS RIOS</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>BOOKCOMPUTER</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>76.376.530-k</t>
         </is>
       </c>
       <c r="K137" t="inlineStr"/>
@@ -8808,13 +8808,13 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>4145.48</v>
+        <v>3065.34</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>975-51-CM26</t>
+          <t>3447-450-CM26</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -8834,32 +8834,32 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Cancelada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>69.265.100-6</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>MUNICIPALIDAD DE ALTO HOSPICIO</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER</t>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>76.376.530-k</t>
+          <t>77.474.803-2</t>
         </is>
       </c>
       <c r="K138" t="inlineStr"/>
@@ -8869,13 +8869,13 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>44723.9</v>
+        <v>17612</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>4494-79-CM26</t>
+          <t>3285-73-CM26</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -8895,32 +8895,32 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>69.150.500-6</t>
+          <t>69.231.000-4</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PENCO</t>
+          <t>I MUNICIPALIDAD DE CURACO DE VELEZ</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>SOC INFORMATICA SIGLO 21 LIMITADA</t>
+          <t>Sumatec Ltda.</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>76.179.170-2</t>
+          <t>76.367.430-4</t>
         </is>
       </c>
       <c r="K139" t="inlineStr"/>
@@ -8930,13 +8930,13 @@
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>6918.66</v>
+        <v>1937.08</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>1057545-161-CM26</t>
+          <t>1395-84-CM26</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -8961,27 +8961,27 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>61.607.500-4</t>
+          <t>61.606.400-2</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD LOS RIOS</t>
+          <t>SERVICIO DE SALUD COQUIMBO</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>76.376.530-k</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K140" t="inlineStr"/>
@@ -8991,13 +8991,13 @@
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>3065.34</v>
+        <v>4263.44</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>3447-450-CM26</t>
+          <t>2791-21-CM26</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -9017,32 +9017,32 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>69.265.100-6</t>
+          <t>69.255.400-0</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE ALTO HOSPICIO</t>
+          <t>Iluste Municipalidad de Huechuraba</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>77.474.803-2</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K141" t="inlineStr"/>
@@ -9052,13 +9052,13 @@
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>17612</v>
+        <v>40031.6</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>3285-73-CM26</t>
+          <t>2676-131-CM26</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -9073,37 +9073,37 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>69.231.000-4</t>
+          <t>69.255.500-7</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CURACO DE VELEZ</t>
+          <t>I MUNICIPALIDAD DE INDEPENDENCIA</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>Sumatec Ltda.</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>76.367.430-4</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K142" t="inlineStr"/>
@@ -9113,13 +9113,13 @@
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>1937.08</v>
+        <v>8675.1</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>1395-84-CM26</t>
+          <t>603663-29-CM26</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -9134,7 +9134,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -9144,27 +9144,27 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>61.606.400-2</t>
+          <t>65.028.707-K</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO</t>
+          <t>INSTITUTO NACIONAL DE DERECHOS HUMANOS</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K143" t="inlineStr"/>
@@ -9174,13 +9174,13 @@
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>4263.44</v>
+        <v>13307.53</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2791-21-CM26</t>
+          <t>1422032-10-CM26</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -9195,37 +9195,37 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>69.255.400-0</t>
+          <t>65.035.343-9</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Iluste Municipalidad de Huechuraba</t>
+          <t>CORPORACION REGIONAL DE DESARROLLO PRODUCTIVO DE LA REGION DE LOS RIOS</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K144" t="inlineStr"/>
@@ -9235,13 +9235,13 @@
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>40031.6</v>
+        <v>1218.46</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2676-131-CM26</t>
+          <t>3921-91-CM26</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -9266,27 +9266,27 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>69.255.500-7</t>
+          <t>69.191.500-K</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE INDEPENDENCIA</t>
+          <t>I MUNICIPALIDAD DE VILLARRICA</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>PC FACTORY</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>78.885.550-8</t>
         </is>
       </c>
       <c r="K145" t="inlineStr"/>
@@ -9296,13 +9296,13 @@
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>8675.1</v>
+        <v>4848.06</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>603663-29-CM26</t>
+          <t>14-76-CM26</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -9327,12 +9327,12 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>65.028.707-K</t>
+          <t>60.703.000-6</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DERECHOS HUMANOS</t>
+          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -9357,13 +9357,13 @@
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>13307.53</v>
+        <v>3459.33</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>1422032-10-CM26</t>
+          <t>14-75-CM26</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -9388,27 +9388,27 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>65.035.343-9</t>
+          <t>60.703.000-6</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>CORPORACION REGIONAL DE DESARROLLO PRODUCTIVO DE LA REGION DE LOS RIOS</t>
+          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K147" t="inlineStr"/>
@@ -9418,13 +9418,13 @@
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>1218.46</v>
+        <v>10174.5</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>3921-91-CM26</t>
+          <t>14-74-CM26</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -9444,32 +9444,32 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>69.191.500-K</t>
+          <t>60.703.000-6</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VILLARRICA</t>
+          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>PC FACTORY</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>78.885.550-8</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K148" t="inlineStr"/>
@@ -9479,13 +9479,13 @@
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>4848.06</v>
+        <v>4680.27</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>14-76-CM26</t>
+          <t>14-73-CM26</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -9540,13 +9540,13 @@
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>3459.33</v>
+        <v>1017.45</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>14-75-CM26</t>
+          <t>14-72-CM26</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -9601,13 +9601,13 @@
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>10174.5</v>
+        <v>3154.1</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>14-74-CM26</t>
+          <t>2440-129-CM26</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -9627,32 +9627,32 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>60.703.000-6</t>
+          <t>69.100.100-8</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
+          <t>I MUNICIPALIDAD DE CURICO</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K151" t="inlineStr"/>
@@ -9662,13 +9662,13 @@
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>4680.27</v>
+        <v>19752.48</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>14-73-CM26</t>
+          <t>4283-50-CM26</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -9688,32 +9688,32 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>60.703.000-6</t>
+          <t>69.050.900-8</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
+          <t>I MUNICIPALIDAD DE CATEMU</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>BOOKCOMPUTER</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>76.376.530-k</t>
         </is>
       </c>
       <c r="K152" t="inlineStr"/>
@@ -9723,13 +9723,13 @@
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>1017.45</v>
+        <v>3337.89</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>14-72-CM26</t>
+          <t>2013-223-CM26</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -9749,32 +9749,32 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>60.703.000-6</t>
+          <t>70.777.500-9</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
+          <t>UNIVERSIDAD ARTURO PRAT</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>COMPUTACION E INGENIERIA S A</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>96.693.120-5</t>
         </is>
       </c>
       <c r="K153" t="inlineStr"/>
@@ -9784,13 +9784,13 @@
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>3154.1</v>
+        <v>74380.95</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>2440-129-CM26</t>
+          <t>937232-177-CM26</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -9810,32 +9810,32 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>69.100.100-8</t>
+          <t>61.980.620-4</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CURICO</t>
+          <t>Centro de Referencia de Salud Hospital Provincia Cordillera</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K154" t="inlineStr"/>
@@ -9845,13 +9845,13 @@
         </is>
       </c>
       <c r="M154" s="2" t="n">
-        <v>19752.48</v>
+        <v>1046.61</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>4283-50-CM26</t>
+          <t>1456839-19-CM26</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -9871,32 +9871,32 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>69.050.900-8</t>
+          <t>61.981.420-7</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CATEMU</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA LOS COPIHUES</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>76.376.530-k</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K155" t="inlineStr"/>
@@ -9906,13 +9906,13 @@
         </is>
       </c>
       <c r="M155" s="2" t="n">
-        <v>3337.89</v>
+        <v>18073.48</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>2013-223-CM26</t>
+          <t>711841-58-CM26</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -9932,32 +9932,32 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>70.777.500-9</t>
+          <t>60.103.000-4</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD ARTURO PRAT</t>
+          <t>SUBSECRETARIA DE SERVICIOS SOCIALES</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>COMPUTACION E INGENIERIA S A</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>96.693.120-5</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K156" t="inlineStr"/>
@@ -9967,13 +9967,13 @@
         </is>
       </c>
       <c r="M156" s="2" t="n">
-        <v>74380.95</v>
+        <v>16279.2</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>937232-177-CM26</t>
+          <t>711841-57-CM26</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -9998,12 +9998,12 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>61.980.620-4</t>
+          <t>60.103.000-4</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Centro de Referencia de Salud Hospital Provincia Cordillera</t>
+          <t>SUBSECRETARIA DE SERVICIOS SOCIALES</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -10013,12 +10013,12 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K157" t="inlineStr"/>
@@ -10028,13 +10028,13 @@
         </is>
       </c>
       <c r="M157" s="2" t="n">
-        <v>1046.61</v>
+        <v>77611.5</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>1456839-19-CM26</t>
+          <t>2484-22-CM26</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -10054,17 +10054,17 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>61.981.420-7</t>
+          <t>69.071.301-2</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA LOS COPIHUES</t>
+          <t>I MUNICIPALIDAD DE QUILICURA</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -10074,12 +10074,12 @@
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>Sumatec Ltda.</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>76.367.430-4</t>
         </is>
       </c>
       <c r="K158" t="inlineStr"/>
@@ -10089,13 +10089,13 @@
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>18073.48</v>
+        <v>3215.14</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>711841-58-CM26</t>
+          <t>2484-21-CM26</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -10115,17 +10115,17 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>60.103.000-4</t>
+          <t>69.071.301-2</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SERVICIOS SOCIALES</t>
+          <t>I MUNICIPALIDAD DE QUILICURA</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -10135,12 +10135,12 @@
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>FRANCO</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>76.139.769-9</t>
         </is>
       </c>
       <c r="K159" t="inlineStr"/>
@@ -10150,13 +10150,13 @@
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>16279.2</v>
+        <v>7393.47</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>711841-57-CM26</t>
+          <t>1549-306-CM26</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -10181,12 +10181,12 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>60.103.000-4</t>
+          <t>61.608.002-4</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SERVICIOS SOCIALES</t>
+          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -10196,12 +10196,12 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>BOOKCOMPUTER</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.376.530-k</t>
         </is>
       </c>
       <c r="K160" t="inlineStr"/>
@@ -10211,13 +10211,13 @@
         </is>
       </c>
       <c r="M160" s="2" t="n">
-        <v>77611.5</v>
+        <v>862.63</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>2484-22-CM26</t>
+          <t>14-71-CM26</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -10237,17 +10237,17 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>69.071.301-2</t>
+          <t>60.703.000-6</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE QUILICURA</t>
+          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -10257,12 +10257,12 @@
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>Sumatec Ltda.</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>76.367.430-4</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K161" t="inlineStr"/>
@@ -10272,13 +10272,13 @@
         </is>
       </c>
       <c r="M161" s="2" t="n">
-        <v>3215.14</v>
+        <v>3052.35</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>2484-21-CM26</t>
+          <t>1084156-116-CM26</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -10293,37 +10293,37 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>69.071.301-2</t>
+          <t>65.181.672-6</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE QUILICURA</t>
+          <t>SERVICIO LOCAL DE EDUCACION PUBLICA ANDALIEN SUR</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Bío-Bío</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>FRANCO</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>76.139.769-9</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K162" t="inlineStr"/>
@@ -10333,13 +10333,13 @@
         </is>
       </c>
       <c r="M162" s="2" t="n">
-        <v>7393.47</v>
+        <v>12198.57</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>1549-306-CM26</t>
+          <t>1305552-28-CM26</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -10354,7 +10354,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -10364,12 +10364,12 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>61.608.002-4</t>
+          <t>61.981.030-9</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA TAMARUGAL</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -10379,12 +10379,12 @@
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER</t>
+          <t>COMERCIALIZADORA TODOCLICK SPA</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>76.376.530-k</t>
+          <t>76.977.985-K</t>
         </is>
       </c>
       <c r="K163" t="inlineStr"/>
@@ -10394,13 +10394,13 @@
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>862.63</v>
+        <v>12944.57</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>14-71-CM26</t>
+          <t>1456838-14-CM26</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -10415,7 +10415,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -10425,12 +10425,12 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>60.703.000-6</t>
+          <t>61.981.440-1</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA LOS CEREZOS</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -10440,12 +10440,12 @@
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>77.108.316-1</t>
         </is>
       </c>
       <c r="K164" t="inlineStr"/>
@@ -10455,13 +10455,13 @@
         </is>
       </c>
       <c r="M164" s="2" t="n">
-        <v>3052.35</v>
+        <v>2772.11</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>1084156-116-CM26</t>
+          <t>1456838-15-CM26</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -10486,27 +10486,27 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>65.181.672-6</t>
+          <t>61.981.440-1</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION PUBLICA ANDALIEN SUR</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA LOS CEREZOS</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>77.108.316-1</t>
         </is>
       </c>
       <c r="K165" t="inlineStr"/>
@@ -10516,13 +10516,13 @@
         </is>
       </c>
       <c r="M165" s="2" t="n">
-        <v>12198.57</v>
+        <v>1933.75</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>1305552-28-CM26</t>
+          <t>1456838-12-CM26</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -10547,12 +10547,12 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>61.981.030-9</t>
+          <t>61.981.440-1</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA TAMARUGAL</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA LOS CEREZOS</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -10562,12 +10562,12 @@
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TODOCLICK SPA</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>76.977.985-K</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K166" t="inlineStr"/>
@@ -10577,13 +10577,13 @@
         </is>
       </c>
       <c r="M166" s="2" t="n">
-        <v>12944.57</v>
+        <v>57695.27</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>1456838-14-CM26</t>
+          <t>1305552-26-CM26</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -10608,12 +10608,12 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>61.981.440-1</t>
+          <t>61.981.030-9</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA LOS CEREZOS</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA TAMARUGAL</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -10623,12 +10623,12 @@
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
+          <t>BOOKCOMPUTER</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>77.108.316-1</t>
+          <t>76.376.530-k</t>
         </is>
       </c>
       <c r="K167" t="inlineStr"/>
@@ -10638,13 +10638,13 @@
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>2772.11</v>
+        <v>11016.41</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>1456838-15-CM26</t>
+          <t>1456838-13-CM26</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -10684,12 +10684,12 @@
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
+          <t>Sociedad Comercial Infostore Ltda</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>77.108.316-1</t>
+          <t>76.131.929-9</t>
         </is>
       </c>
       <c r="K168" t="inlineStr"/>
@@ -10699,13 +10699,13 @@
         </is>
       </c>
       <c r="M168" s="2" t="n">
-        <v>1933.75</v>
+        <v>3058.06</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>1456838-12-CM26</t>
+          <t>4751-21-CM26</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -10720,37 +10720,37 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>61.981.440-1</t>
+          <t>69.091.400-K</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA LOS CEREZOS</t>
+          <t>I MUNICIPALIDAD DE LA ESTRELLA</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Lib. Gral. Bdo. O'Higgins</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K169" t="inlineStr"/>
@@ -10760,13 +10760,13 @@
         </is>
       </c>
       <c r="M169" s="2" t="n">
-        <v>57695.27</v>
+        <v>19646.6</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>1305552-26-CM26</t>
+          <t>2546-141-CM26</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -10781,37 +10781,37 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>61.981.030-9</t>
+          <t>61.955.000-5</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA TAMARUGAL</t>
+          <t>I MUNICIPALIDAD DE PADRE LAS CASAS</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER</t>
+          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>76.376.530-k</t>
+          <t>96.523.180-3</t>
         </is>
       </c>
       <c r="K170" t="inlineStr"/>
@@ -10821,13 +10821,13 @@
         </is>
       </c>
       <c r="M170" s="2" t="n">
-        <v>11016.41</v>
+        <v>2100.11</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>1456838-13-CM26</t>
+          <t>1480111-1-CM26</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -10842,7 +10842,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
@@ -10852,12 +10852,12 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>61.981.440-1</t>
+          <t>69.255.600-3</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA LOS CEREZOS</t>
+          <t>MUNICIPALIDAD DE VITACURA</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>Sociedad Comercial Infostore Ltda</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>76.131.929-9</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K171" t="inlineStr"/>
@@ -10882,13 +10882,13 @@
         </is>
       </c>
       <c r="M171" s="2" t="n">
-        <v>3058.06</v>
+        <v>659.08</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>4751-21-CM26</t>
+          <t>4112-14-CM26</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -10908,32 +10908,32 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>69.091.400-K</t>
+          <t>69.181.000-3</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA ESTRELLA</t>
+          <t>I MUNICIPALIDAD DE CURACAUTIN</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>76.416.101-7</t>
         </is>
       </c>
       <c r="K172" t="inlineStr"/>
@@ -10943,13 +10943,13 @@
         </is>
       </c>
       <c r="M172" s="2" t="n">
-        <v>19646.6</v>
+        <v>2022.11</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>2546-141-CM26</t>
+          <t>4112-15-CM26</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -10969,17 +10969,17 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>61.955.000-5</t>
+          <t>69.181.000-3</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PADRE LAS CASAS</t>
+          <t>I MUNICIPALIDAD DE CURACAUTIN</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -10989,12 +10989,12 @@
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
+          <t>COMPUNOW SPA</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t>96.523.180-3</t>
+          <t>78.218.816-K</t>
         </is>
       </c>
       <c r="K173" t="inlineStr"/>
@@ -11004,13 +11004,13 @@
         </is>
       </c>
       <c r="M173" s="2" t="n">
-        <v>2100.11</v>
+        <v>11797.89</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>1480111-1-CM26</t>
+          <t>3638-88-CM26</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -11030,32 +11030,32 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>69.255.600-3</t>
+          <t>69.250.300-7</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE VITACURA</t>
+          <t>I.MUNICIPALIDAD DE PORVENIR</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Magallanes y Antártica</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K174" t="inlineStr"/>
@@ -11065,13 +11065,13 @@
         </is>
       </c>
       <c r="M174" s="2" t="n">
-        <v>659.08</v>
+        <v>17255</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>4112-14-CM26</t>
+          <t>2698-37-CM26</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -11091,32 +11091,32 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>69.181.000-3</t>
+          <t>69.073.600-4</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CURACAUTIN</t>
+          <t>I MUNICIPALIDAD DE CARTAGENA</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K175" t="inlineStr"/>
@@ -11126,13 +11126,13 @@
         </is>
       </c>
       <c r="M175" s="2" t="n">
-        <v>2022.11</v>
+        <v>3139.82</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>4112-15-CM26</t>
+          <t>2429-167-CM26</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -11152,32 +11152,32 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>69.181.000-3</t>
+          <t>69.020.300-6</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CURACAUTIN</t>
+          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>COMPUNOW SPA</t>
+          <t>Sumatec Ltda.</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
         <is>
-          <t>78.218.816-K</t>
+          <t>76.367.430-4</t>
         </is>
       </c>
       <c r="K176" t="inlineStr"/>
@@ -11187,13 +11187,13 @@
         </is>
       </c>
       <c r="M176" s="2" t="n">
-        <v>11797.89</v>
+        <v>3094.83</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>3638-88-CM26</t>
+          <t>1107276-42-CM26</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -11213,32 +11213,32 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>69.250.300-7</t>
+          <t>61.312.000-9</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>I.MUNICIPALIDAD DE PORVENIR</t>
+          <t>INSTITUTO DE INVESTIGACIONES AGROPECUARIAS</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K177" t="inlineStr"/>
@@ -11248,13 +11248,13 @@
         </is>
       </c>
       <c r="M177" s="2" t="n">
-        <v>17255</v>
+        <v>1461.46</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>2698-37-CM26</t>
+          <t>2211-228-CM26</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -11279,12 +11279,12 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>69.073.600-4</t>
+          <t>69.061.100-7</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CARTAGENA</t>
+          <t>I MUNICIPALIDAD DE LIMACHE</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -11294,12 +11294,12 @@
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K178" t="inlineStr"/>
@@ -11309,13 +11309,13 @@
         </is>
       </c>
       <c r="M178" s="2" t="n">
-        <v>3139.82</v>
+        <v>8143.29</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>2429-167-CM26</t>
+          <t>3634-95-CM26</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -11335,32 +11335,32 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>69.020.300-6</t>
+          <t>69.081.500-1</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
+          <t>I MUNICIPALIDAD DE MALLOA</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Lib. Gral. Bdo. O'Higgins</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>Sumatec Ltda.</t>
+          <t>COMERCIALIZADORA TODOCLICK SPA</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t>76.367.430-4</t>
+          <t>76.977.985-K</t>
         </is>
       </c>
       <c r="K179" t="inlineStr"/>
@@ -11370,13 +11370,13 @@
         </is>
       </c>
       <c r="M179" s="2" t="n">
-        <v>3094.83</v>
+        <v>6171.7</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>1107276-42-CM26</t>
+          <t>1475050-21-CM26</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -11391,7 +11391,7 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>61.312.000-9</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>INSTITUTO DE INVESTIGACIONES AGROPECUARIAS</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -11416,12 +11416,12 @@
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>COMPUNOW SPA</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>78.218.816-K</t>
         </is>
       </c>
       <c r="K180" t="inlineStr"/>
@@ -11431,13 +11431,13 @@
         </is>
       </c>
       <c r="M180" s="2" t="n">
-        <v>1461.46</v>
+        <v>4361.68</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>2211-228-CM26</t>
+          <t>1528-20-CM26</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -11452,22 +11452,22 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>69.061.100-7</t>
+          <t>60.511.052-5</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LIMACHE</t>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE QUILLOTA</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -11477,12 +11477,12 @@
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>77.108.316-1</t>
         </is>
       </c>
       <c r="K181" t="inlineStr"/>
@@ -11492,13 +11492,13 @@
         </is>
       </c>
       <c r="M181" s="2" t="n">
-        <v>8143.29</v>
+        <v>1514.79</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>3634-95-CM26</t>
+          <t>4377-67-CM26</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -11513,37 +11513,37 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>69.081.500-1</t>
+          <t>69.151.100-6</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MALLOA</t>
+          <t>I MUNICIPALIDAD DE SAN ROSENDO</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>Bío-Bío</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TODOCLICK SPA</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>76.977.985-K</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K182" t="inlineStr"/>
@@ -11553,13 +11553,13 @@
         </is>
       </c>
       <c r="M182" s="2" t="n">
-        <v>6171.7</v>
+        <v>7777.55</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>1475050-21-CM26</t>
+          <t>2404-218-CM26</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -11579,22 +11579,22 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>69.010.300-1</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>I MUNICIPALIDAD DE IQUIQUE</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -11614,13 +11614,13 @@
         </is>
       </c>
       <c r="M183" s="2" t="n">
-        <v>4361.68</v>
+        <v>32034.5</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>1528-20-CM26</t>
+          <t>2404-209-CM26</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -11640,32 +11640,32 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>60.511.052-5</t>
+          <t>69.010.300-1</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE QUILLOTA</t>
+          <t>I MUNICIPALIDAD DE IQUIQUE</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
         <is>
-          <t>77.108.316-1</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K184" t="inlineStr"/>
@@ -11675,13 +11675,13 @@
         </is>
       </c>
       <c r="M184" s="2" t="n">
-        <v>1514.79</v>
+        <v>4389.09</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>4377-67-CM26</t>
+          <t>2577-12-CM26</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -11701,32 +11701,32 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>69.151.100-6</t>
+          <t>69.070.100-6</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN ROSENDO</t>
+          <t>I MUNICIPALIDAD DE SANTIAGO</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>Tic Services SPA</t>
         </is>
       </c>
       <c r="J185" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>76.423.634-3</t>
         </is>
       </c>
       <c r="K185" t="inlineStr"/>
@@ -11736,13 +11736,13 @@
         </is>
       </c>
       <c r="M185" s="2" t="n">
-        <v>7777.55</v>
+        <v>3067.82</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>2404-218-CM26</t>
+          <t>4284-92-CM26</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -11762,32 +11762,32 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>69.010.300-1</t>
+          <t>69.191.000-8</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE IQUIQUE</t>
+          <t>I MUNICIPALIDAD DE CUNCO</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>COMPUNOW SPA</t>
+          <t>PC FACTORY</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
         <is>
-          <t>78.218.816-K</t>
+          <t>78.885.550-8</t>
         </is>
       </c>
       <c r="K186" t="inlineStr"/>
@@ -11797,189 +11797,6 @@
         </is>
       </c>
       <c r="M186" s="2" t="n">
-        <v>32034.5</v>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="inlineStr">
-        <is>
-          <t>2404-209-CM26</t>
-        </is>
-      </c>
-      <c r="B187" t="inlineStr">
-        <is>
-          <t>2239-5-LR25</t>
-        </is>
-      </c>
-      <c r="C187" t="inlineStr">
-        <is>
-          <t>feb-2026</t>
-        </is>
-      </c>
-      <c r="D187" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="E187" t="inlineStr">
-        <is>
-          <t>Aceptada</t>
-        </is>
-      </c>
-      <c r="F187" t="inlineStr">
-        <is>
-          <t>69.010.300-1</t>
-        </is>
-      </c>
-      <c r="G187" t="inlineStr">
-        <is>
-          <t>I MUNICIPALIDAD DE IQUIQUE</t>
-        </is>
-      </c>
-      <c r="H187" t="inlineStr">
-        <is>
-          <t>Tarapacá</t>
-        </is>
-      </c>
-      <c r="I187" t="inlineStr">
-        <is>
-          <t>LECHNER S.A</t>
-        </is>
-      </c>
-      <c r="J187" t="inlineStr">
-        <is>
-          <t>78.114.650-1</t>
-        </is>
-      </c>
-      <c r="K187" t="inlineStr"/>
-      <c r="L187" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M187" s="2" t="n">
-        <v>4389.09</v>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="inlineStr">
-        <is>
-          <t>2577-12-CM26</t>
-        </is>
-      </c>
-      <c r="B188" t="inlineStr">
-        <is>
-          <t>2239-5-LR25</t>
-        </is>
-      </c>
-      <c r="C188" t="inlineStr">
-        <is>
-          <t>feb-2026</t>
-        </is>
-      </c>
-      <c r="D188" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="E188" t="inlineStr">
-        <is>
-          <t>Recepcion Conforme</t>
-        </is>
-      </c>
-      <c r="F188" t="inlineStr">
-        <is>
-          <t>69.070.100-6</t>
-        </is>
-      </c>
-      <c r="G188" t="inlineStr">
-        <is>
-          <t>I MUNICIPALIDAD DE SANTIAGO</t>
-        </is>
-      </c>
-      <c r="H188" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
-      <c r="I188" t="inlineStr">
-        <is>
-          <t>Tic Services SPA</t>
-        </is>
-      </c>
-      <c r="J188" t="inlineStr">
-        <is>
-          <t>76.423.634-3</t>
-        </is>
-      </c>
-      <c r="K188" t="inlineStr"/>
-      <c r="L188" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M188" s="2" t="n">
-        <v>3067.82</v>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="inlineStr">
-        <is>
-          <t>4284-92-CM26</t>
-        </is>
-      </c>
-      <c r="B189" t="inlineStr">
-        <is>
-          <t>2239-5-LR25</t>
-        </is>
-      </c>
-      <c r="C189" t="inlineStr">
-        <is>
-          <t>feb-2026</t>
-        </is>
-      </c>
-      <c r="D189" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="E189" t="inlineStr">
-        <is>
-          <t>Recepcion Conforme</t>
-        </is>
-      </c>
-      <c r="F189" t="inlineStr">
-        <is>
-          <t>69.191.000-8</t>
-        </is>
-      </c>
-      <c r="G189" t="inlineStr">
-        <is>
-          <t>I MUNICIPALIDAD DE CUNCO</t>
-        </is>
-      </c>
-      <c r="H189" t="inlineStr">
-        <is>
-          <t>Araucanía</t>
-        </is>
-      </c>
-      <c r="I189" t="inlineStr">
-        <is>
-          <t>PC FACTORY</t>
-        </is>
-      </c>
-      <c r="J189" t="inlineStr">
-        <is>
-          <t>78.885.550-8</t>
-        </is>
-      </c>
-      <c r="K189" t="inlineStr"/>
-      <c r="L189" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M189" s="2" t="n">
         <v>2342.28</v>
       </c>
     </row>
